--- a/wk4/Xlookup.xlsx
+++ b/wk4/Xlookup.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\instructor-dab-sep-2026\wk4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk4/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEC644BB-0E91-4263-8353-BF16A4599D35}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B8A2F5F-2677-DE44-B871-2A4AC1D09D28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="360" windowWidth="23304" windowHeight="12504" xr2:uid="{093018B4-BD74-45BA-99AD-4BE372E656CD}"/>
+    <workbookView xWindow="-31360" yWindow="-4220" windowWidth="38400" windowHeight="21000" activeTab="2" xr2:uid="{093018B4-BD74-45BA-99AD-4BE372E656CD}"/>
   </bookViews>
   <sheets>
     <sheet name="Background" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -59,13 +59,30 @@
 </metadata>
 </file>
 
+<file path=xl/python.xml><?xml version="1.0" encoding="utf-8"?>
+<python xmlns="http://schemas.microsoft.com/office/spreadsheetml/2023/python">
+  <environmentDefinition id="{882DD1B0-6546-4DFA-8A08-902A380B44EA}">
+    <initialization>
+      <code xml:space="preserve">import numpy as np
+import pandas as pd
+import matplotlib.pyplot as plt
+import seaborn as sns
+import statsmodels as sm
+import excel
+import warnings
+warnings.simplefilter('ignore')
+excel.set_xl_scalar_conversion(excel.convert_to_scalar)
+excel.set_xl_array_conversion(excel.convert_to_dataframe)
+</code>
+    </initialization>
+  </environmentDefinition>
+</python>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="73">
   <si>
     <t>Feature</t>
-  </si>
-  <si>
-    <t>VLOOKUP</t>
   </si>
   <si>
     <t>INDEX MATCH</t>
@@ -511,6 +528,18 @@
   </si>
   <si>
     <t>Task C: Solving it with XLOOKUP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">  </t>
+  </si>
+  <si>
+    <t>match()</t>
+  </si>
+  <si>
+    <t>index()</t>
+  </si>
+  <si>
+    <t>"this is wrong value"</t>
   </si>
 </sst>
 </file>
@@ -587,12 +616,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -622,7 +657,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -662,6 +697,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2721,17 +2757,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99847E35-01CC-4CA3-B422-D7BD48FF328C}">
   <dimension ref="N2:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="14" max="14" width="16.77734375" customWidth="1"/>
-    <col min="15" max="15" width="18.88671875" customWidth="1"/>
-    <col min="16" max="16" width="21.88671875" customWidth="1"/>
+    <col min="14" max="14" width="16.83203125" customWidth="1"/>
+    <col min="15" max="15" width="18.83203125" customWidth="1"/>
+    <col min="16" max="16" width="21.83203125" customWidth="1"/>
     <col min="17" max="17" width="20.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="14:17">
       <c r="N2" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="14:17">
@@ -2739,97 +2775,97 @@
         <v>0</v>
       </c>
       <c r="O3" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="P3" s="6" t="s">
         <v>1</v>
       </c>
-      <c r="P3" s="6" t="s">
+      <c r="Q3" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="Q3" s="6" t="s">
+    </row>
+    <row r="4" spans="14:17" ht="30">
+      <c r="N4" s="2" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="4" spans="14:17" ht="27.6">
-      <c r="N4" s="2" t="s">
+      <c r="O4" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="P4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="Q4" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="Q4" s="5" t="s">
+    </row>
+    <row r="5" spans="14:17" ht="30">
+      <c r="N5" s="2" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="14:17" ht="27.6">
-      <c r="N5" s="2" t="s">
+      <c r="O5" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="P5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="P5" s="2" t="s">
+      <c r="Q5" s="3" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="14:17" ht="45">
+      <c r="N6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="Q5" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="14:17" ht="55.2">
-      <c r="N6" s="2" t="s">
+      <c r="O6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="O6" s="2" t="s">
+      <c r="P6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="P6" s="2" t="s">
+      <c r="Q6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="Q6" s="3" t="s">
+    </row>
+    <row r="7" spans="14:17" ht="45">
+      <c r="N7" s="2" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="7" spans="14:17" ht="41.4">
-      <c r="N7" s="2" t="s">
+      <c r="O7" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="P7" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="Q7" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="14:17" ht="60">
+      <c r="N8" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="Q7" s="5" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="8" spans="14:17" ht="55.2">
-      <c r="N8" s="2" t="s">
+      <c r="O8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="P8" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="Q8" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="5" t="s">
+    </row>
+    <row r="9" spans="14:17" ht="45">
+      <c r="N9" s="2" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="14:17" ht="41.4">
-      <c r="N9" s="2" t="s">
+      <c r="O9" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="P9" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="Q9" s="5" t="s">
         <v>23</v>
-      </c>
-      <c r="P9" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q9" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -2841,69 +2877,73 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{838E53BD-C599-4953-B76F-8E1B3C7A5BCE}">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13.5546875" customWidth="1"/>
-    <col min="2" max="2" width="20.88671875" customWidth="1"/>
-    <col min="3" max="3" width="11.88671875" customWidth="1"/>
+    <col min="1" max="1" width="13.5" customWidth="1"/>
+    <col min="2" max="2" width="20.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
     <col min="4" max="4" width="11" customWidth="1"/>
-    <col min="7" max="7" width="34.5546875" customWidth="1"/>
-    <col min="8" max="8" width="30.21875" customWidth="1"/>
+    <col min="7" max="7" width="34.5" customWidth="1"/>
+    <col min="8" max="8" width="30.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="23.4">
+    <row r="1" spans="1:7" ht="24">
       <c r="A1" s="7" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="C5" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="D5" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>41</v>
-      </c>
       <c r="G5" s="8" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="16">
       <c r="A6" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>27</v>
       </c>
-      <c r="B6" s="9" t="s">
+      <c r="C6" s="9" t="s">
         <v>28</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>29</v>
       </c>
       <c r="D6" s="10">
         <v>1200</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="G6">
+        <f>VLOOKUP(A11,A5:D9,4,FALSE)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="7" spans="1:7">
       <c r="A7" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B7" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="9" t="s">
-        <v>31</v>
-      </c>
       <c r="C7" s="9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="D7" s="10">
         <v>800</v>
@@ -2911,13 +2951,13 @@
     </row>
     <row r="8" spans="1:7">
       <c r="A8" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B8" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B8" s="9" t="s">
+      <c r="C8" s="9" t="s">
         <v>33</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>34</v>
       </c>
       <c r="D8" s="10">
         <v>350</v>
@@ -2925,52 +2965,78 @@
     </row>
     <row r="9" spans="1:7">
       <c r="A9" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>36</v>
-      </c>
-      <c r="C9" s="9" t="s">
-        <v>37</v>
       </c>
       <c r="D9" s="10">
         <v>80</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:7">
       <c r="F10" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="G10" cm="1">
+        <f t="array" ref="G10">INDEX(D5:D9,MATCH(A11,A5:A9,0),0)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="11" spans="1:7">
       <c r="A11" s="12" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="F12" t="s">
+        <v>70</v>
+      </c>
+      <c r="G12">
+        <f>MATCH(A11,A5:A9,0)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="F13" t="s">
+        <v>71</v>
+      </c>
+      <c r="G13" cm="1">
+        <f t="array" ref="G13">INDEX(D5:D9,G12,0)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="16" spans="1:7">
       <c r="G16" s="8" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="14" t="s">
-        <v>44</v>
+        <v>43</v>
+      </c>
+      <c r="G17">
+        <f>_xlfn.XLOOKUP(A11,A5:A9,D5:D9,"false",0,1)</f>
+        <v>800</v>
       </c>
     </row>
     <row r="20" spans="6:7">
       <c r="G20" s="8" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="6:7">
       <c r="G21" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -2980,98 +3046,111 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4DFBF716-6882-46EE-ADD2-64AA7C7F3F2B}">
-  <dimension ref="A1:F16"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <dimension ref="A1:G18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.88671875" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
     <col min="2" max="2" width="17" customWidth="1"/>
-    <col min="3" max="3" width="17.88671875" customWidth="1"/>
-    <col min="6" max="6" width="11.88671875" customWidth="1"/>
+    <col min="3" max="3" width="17.83203125" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="23.4">
+    <row r="1" spans="1:7" ht="24">
       <c r="A1" s="7" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3" s="8" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="8" t="s">
+    <row r="5" spans="1:7">
+      <c r="A5" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>62</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6" s="9" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="6" t="s">
-        <v>61</v>
-      </c>
-      <c r="B5" s="6" t="s">
-        <v>62</v>
-      </c>
-      <c r="C5" s="6" t="s">
+      <c r="B6" s="9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="F7" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="B8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="F9" t="str">
+        <f>VLOOKUP(A10,A5:C8,1,TRUE)</f>
+        <v>John Doe</v>
+      </c>
+      <c r="G9" s="15" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
         <v>63</v>
       </c>
-      <c r="F5" s="8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>53</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="F6" s="8" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="9" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="9" t="s">
-        <v>56</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="F7" t="s">
+    </row>
+    <row r="12" spans="1:7">
+      <c r="F12" s="8" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="B8" s="9" t="s">
-        <v>59</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="B10" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="F12" s="8" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
+    <row r="14" spans="1:7">
       <c r="A14" t="str">
         <f ca="1">+_xlfn.FORMULATEXT(A15)</f>
         <v>=XLOOKUP(A10, B6:B8, A6:C8)</v>
       </c>
-    </row>
-    <row r="15" spans="1:6">
+      <c r="F14" t="str">
+        <f>INDEX(A5:A8,MATCH(A10,B5:B8,0))</f>
+        <v>Maria Santos</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7">
       <c r="A15" t="str" cm="1">
         <f t="array" ref="A15:C15">_xlfn.XLOOKUP(A10, B6:B8, A6:C8)</f>
         <v>Maria Santos</v>
@@ -3083,9 +3162,15 @@
         <v>Operations</v>
       </c>
     </row>
-    <row r="16" spans="1:6">
+    <row r="16" spans="1:7">
       <c r="F16" s="8" t="s">
-        <v>69</v>
+        <v>68</v>
+      </c>
+    </row>
+    <row r="18" spans="6:6">
+      <c r="F18" t="str">
+        <f>_xlfn.XLOOKUP(A10,B5:B8,A5:A8,"False",0,1)</f>
+        <v>Maria Santos</v>
       </c>
     </row>
   </sheetData>
